--- a/data/leveloggers/Devereux_Slough_mouth_state.xlsx
+++ b/data/leveloggers/Devereux_Slough_mouth_state.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ccber_work/Documents/GitHub/hydrology/data/leveloggers/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C23270E2-DAE6-8F46-B19D-A1A455153B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0A04BD-9952-9C40-953B-3551964E073D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9880" yWindow="660" windowWidth="25060" windowHeight="16180" xr2:uid="{0AA5A9BD-0AB9-AC46-8429-5FB4F3CC9E48}"/>
+    <workbookView xWindow="4540" yWindow="660" windowWidth="25060" windowHeight="16180" xr2:uid="{0AA5A9BD-0AB9-AC46-8429-5FB4F3CC9E48}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$32</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="6">
   <si>
     <t>date</t>
   </si>
@@ -409,7 +412,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5033DF66-57A6-1446-B245-A8A364B51B89}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
@@ -613,7 +616,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>45976</v>
+        <v>45701</v>
       </c>
       <c r="B25" t="s">
         <v>3</v>
@@ -621,7 +624,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>46059</v>
+        <v>45719</v>
       </c>
       <c r="B26" t="s">
         <v>2</v>
@@ -629,7 +632,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>46072</v>
+        <v>45729</v>
       </c>
       <c r="B27" t="s">
         <v>3</v>
@@ -637,13 +640,46 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
+        <v>45732</v>
+      </c>
+      <c r="B28" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="2">
+        <v>45976</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
+        <v>46059</v>
+      </c>
+      <c r="B30" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="2">
+        <v>46072</v>
+      </c>
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
         <v>46088</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B32" t="s">
         <v>2</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C32" xr:uid="{5033DF66-57A6-1446-B245-A8A364B51B89}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>